--- a/output/요금제현황_20260423.xlsx
+++ b/output/요금제현황_20260423.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9947" uniqueCount="1267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9953" uniqueCount="1268">
   <si>
     <t>회사명</t>
   </si>
@@ -3380,6 +3380,9 @@
   </si>
   <si>
     <t>초알뜰 1GB/100분</t>
+  </si>
+  <si>
+    <t>비노출</t>
   </si>
   <si>
     <t>초알뜰 2GB/100분</t>
@@ -3821,7 +3824,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -3835,6 +3838,16 @@
       <sz val="10"/>
     </font>
     <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF999999"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF808080"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -3877,7 +3890,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3911,6 +3924,36 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -42684,126 +42727,126 @@
       </c>
     </row>
     <row r="938" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A938" s="2" t="s">
+      <c r="A938" s="12" t="s">
         <v>930</v>
       </c>
-      <c r="B938" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C938" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D938" s="2" t="s">
+      <c r="B938" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C938" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="D938" s="12" t="s">
         <v>1122</v>
       </c>
-      <c r="E938" s="2" t="s">
+      <c r="E938" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F938" s="2" t="s">
+      <c r="F938" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="G938" s="3">
+      <c r="G938" s="13">
         <v>1</v>
       </c>
-      <c r="H938" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I938" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J938" s="4">
-        <v>15400</v>
-      </c>
-      <c r="K938" s="4">
+      <c r="H938" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I938" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J938" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="K938" s="15">
         <v>2900</v>
       </c>
-      <c r="L938" s="4">
-        <v>2900</v>
-      </c>
-      <c r="M938" s="5" t="s">
-        <v>20</v>
+      <c r="L938" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="M938" s="16" t="s">
+        <v>1123</v>
       </c>
     </row>
     <row r="939" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A939" s="6" t="s">
+      <c r="A939" s="17" t="s">
         <v>930</v>
       </c>
-      <c r="B939" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C939" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="D939" s="6" t="s">
+      <c r="B939" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C939" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="D939" s="17" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E939" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="F939" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="G939" s="18">
+        <v>2</v>
+      </c>
+      <c r="H939" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="I939" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="J939" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="K939" s="20">
+        <v>3900</v>
+      </c>
+      <c r="L939" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="M939" s="21" t="s">
         <v>1123</v>
       </c>
-      <c r="E939" s="6" t="s">
+    </row>
+    <row r="940" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A940" s="12" t="s">
+        <v>930</v>
+      </c>
+      <c r="B940" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C940" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="D940" s="12" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E940" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F939" s="6" t="s">
+      <c r="F940" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="G939" s="7">
-        <v>2</v>
-      </c>
-      <c r="H939" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I939" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J939" s="8">
-        <v>18500</v>
-      </c>
-      <c r="K939" s="8">
-        <v>3900</v>
-      </c>
-      <c r="L939" s="8">
-        <v>3900</v>
-      </c>
-      <c r="M939" s="9" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="940" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A940" s="2" t="s">
-        <v>930</v>
-      </c>
-      <c r="B940" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C940" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D940" s="2" t="s">
-        <v>1124</v>
-      </c>
-      <c r="E940" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F940" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G940" s="3">
+      <c r="G940" s="13">
         <v>3</v>
       </c>
-      <c r="H940" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I940" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J940" s="4">
-        <v>20500</v>
-      </c>
-      <c r="K940" s="4">
+      <c r="H940" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="I940" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="J940" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="K940" s="15">
         <v>4900</v>
       </c>
-      <c r="L940" s="4">
-        <v>4900</v>
-      </c>
-      <c r="M940" s="5" t="s">
-        <v>20</v>
+      <c r="L940" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="M940" s="16" t="s">
+        <v>1123</v>
       </c>
     </row>
     <row r="941" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -42817,7 +42860,7 @@
         <v>232</v>
       </c>
       <c r="D941" s="6" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="E941" s="6" t="s">
         <v>95</v>
@@ -42858,7 +42901,7 @@
         <v>232</v>
       </c>
       <c r="D942" s="2" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="E942" s="2" t="s">
         <v>95</v>
@@ -42899,7 +42942,7 @@
         <v>232</v>
       </c>
       <c r="D943" s="6" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E943" s="6" t="s">
         <v>95</v>
@@ -42940,7 +42983,7 @@
         <v>232</v>
       </c>
       <c r="D944" s="2" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="E944" s="2" t="s">
         <v>95</v>
@@ -42981,7 +43024,7 @@
         <v>232</v>
       </c>
       <c r="D945" s="6" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="E945" s="6" t="s">
         <v>95</v>
@@ -43022,7 +43065,7 @@
         <v>232</v>
       </c>
       <c r="D946" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="E946" s="2" t="s">
         <v>95</v>
@@ -43063,7 +43106,7 @@
         <v>232</v>
       </c>
       <c r="D947" s="6" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="E947" s="6" t="s">
         <v>95</v>
@@ -43104,7 +43147,7 @@
         <v>232</v>
       </c>
       <c r="D948" s="2" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="E948" s="2" t="s">
         <v>95</v>
@@ -43145,7 +43188,7 @@
         <v>232</v>
       </c>
       <c r="D949" s="6" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="E949" s="6" t="s">
         <v>95</v>
@@ -43186,7 +43229,7 @@
         <v>232</v>
       </c>
       <c r="D950" s="2" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="E950" s="2" t="s">
         <v>95</v>
@@ -43227,7 +43270,7 @@
         <v>232</v>
       </c>
       <c r="D951" s="6" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="E951" s="6" t="s">
         <v>95</v>
@@ -43268,7 +43311,7 @@
         <v>232</v>
       </c>
       <c r="D952" s="2" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="E952" s="2" t="s">
         <v>821</v>
@@ -43283,7 +43326,7 @@
         <v>19</v>
       </c>
       <c r="I952" s="2" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="J952" s="4">
         <v>9900</v>
@@ -43309,7 +43352,7 @@
         <v>232</v>
       </c>
       <c r="D953" s="6" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="E953" s="6" t="s">
         <v>73</v>
@@ -43350,7 +43393,7 @@
         <v>232</v>
       </c>
       <c r="D954" s="2" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="E954" s="2" t="s">
         <v>73</v>
@@ -43391,7 +43434,7 @@
         <v>232</v>
       </c>
       <c r="D955" s="6" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="E955" s="6" t="s">
         <v>73</v>
@@ -43432,7 +43475,7 @@
         <v>232</v>
       </c>
       <c r="D956" s="2" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="E956" s="2" t="s">
         <v>821</v>
@@ -43473,7 +43516,7 @@
         <v>232</v>
       </c>
       <c r="D957" s="6" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="E957" s="6" t="s">
         <v>821</v>
@@ -43514,7 +43557,7 @@
         <v>232</v>
       </c>
       <c r="D958" s="2" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="E958" s="2" t="s">
         <v>821</v>
@@ -43555,7 +43598,7 @@
         <v>232</v>
       </c>
       <c r="D959" s="6" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="E959" s="6" t="s">
         <v>730</v>
@@ -43596,7 +43639,7 @@
         <v>232</v>
       </c>
       <c r="D960" s="2" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="E960" s="2" t="s">
         <v>95</v>
@@ -43637,7 +43680,7 @@
         <v>232</v>
       </c>
       <c r="D961" s="6" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="E961" s="6" t="s">
         <v>478</v>
@@ -43678,7 +43721,7 @@
         <v>232</v>
       </c>
       <c r="D962" s="2" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="E962" s="2" t="s">
         <v>95</v>
@@ -43710,7 +43753,7 @@
     </row>
     <row r="963" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A963" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B963" s="6" t="s">
         <v>44</v>
@@ -43719,10 +43762,10 @@
         <v>15</v>
       </c>
       <c r="D963" s="6" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="E963" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F963" s="6" t="s">
         <v>25</v>
@@ -43751,7 +43794,7 @@
     </row>
     <row r="964" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A964" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B964" s="2" t="s">
         <v>44</v>
@@ -43760,10 +43803,10 @@
         <v>15</v>
       </c>
       <c r="D964" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E964" s="2" t="s">
         <v>1151</v>
-      </c>
-      <c r="E964" s="2" t="s">
-        <v>1150</v>
       </c>
       <c r="F964" s="2" t="s">
         <v>25</v>
@@ -43792,7 +43835,7 @@
     </row>
     <row r="965" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A965" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B965" s="6" t="s">
         <v>44</v>
@@ -43801,10 +43844,10 @@
         <v>15</v>
       </c>
       <c r="D965" s="6" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="E965" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F965" s="6" t="s">
         <v>25</v>
@@ -43833,7 +43876,7 @@
     </row>
     <row r="966" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A966" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B966" s="2" t="s">
         <v>44</v>
@@ -43842,10 +43885,10 @@
         <v>15</v>
       </c>
       <c r="D966" s="2" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="E966" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F966" s="2" t="s">
         <v>25</v>
@@ -43874,7 +43917,7 @@
     </row>
     <row r="967" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A967" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B967" s="6" t="s">
         <v>44</v>
@@ -43883,10 +43926,10 @@
         <v>15</v>
       </c>
       <c r="D967" s="6" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="E967" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F967" s="6" t="s">
         <v>25</v>
@@ -43915,7 +43958,7 @@
     </row>
     <row r="968" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A968" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B968" s="2" t="s">
         <v>44</v>
@@ -43924,10 +43967,10 @@
         <v>15</v>
       </c>
       <c r="D968" s="2" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="E968" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F968" s="2" t="s">
         <v>25</v>
@@ -43956,7 +43999,7 @@
     </row>
     <row r="969" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A969" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B969" s="6" t="s">
         <v>44</v>
@@ -43965,10 +44008,10 @@
         <v>15</v>
       </c>
       <c r="D969" s="6" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="E969" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F969" s="6" t="s">
         <v>25</v>
@@ -43997,7 +44040,7 @@
     </row>
     <row r="970" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A970" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B970" s="2" t="s">
         <v>44</v>
@@ -44006,10 +44049,10 @@
         <v>15</v>
       </c>
       <c r="D970" s="2" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="E970" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F970" s="2" t="s">
         <v>25</v>
@@ -44038,7 +44081,7 @@
     </row>
     <row r="971" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A971" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B971" s="6" t="s">
         <v>44</v>
@@ -44047,10 +44090,10 @@
         <v>15</v>
       </c>
       <c r="D971" s="6" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="E971" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F971" s="6" t="s">
         <v>25</v>
@@ -44079,7 +44122,7 @@
     </row>
     <row r="972" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A972" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B972" s="2" t="s">
         <v>44</v>
@@ -44088,10 +44131,10 @@
         <v>15</v>
       </c>
       <c r="D972" s="2" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="E972" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F972" s="2" t="s">
         <v>25</v>
@@ -44120,7 +44163,7 @@
     </row>
     <row r="973" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A973" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B973" s="6" t="s">
         <v>44</v>
@@ -44129,10 +44172,10 @@
         <v>15</v>
       </c>
       <c r="D973" s="6" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="E973" s="6" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="F973" s="6" t="s">
         <v>25</v>
@@ -44161,7 +44204,7 @@
     </row>
     <row r="974" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A974" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B974" s="2" t="s">
         <v>44</v>
@@ -44170,10 +44213,10 @@
         <v>15</v>
       </c>
       <c r="D974" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E974" s="2" t="s">
         <v>1162</v>
-      </c>
-      <c r="E974" s="2" t="s">
-        <v>1161</v>
       </c>
       <c r="F974" s="2" t="s">
         <v>25</v>
@@ -44202,7 +44245,7 @@
     </row>
     <row r="975" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A975" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B975" s="6" t="s">
         <v>44</v>
@@ -44211,10 +44254,10 @@
         <v>15</v>
       </c>
       <c r="D975" s="6" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="E975" s="6" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="F975" s="6" t="s">
         <v>69</v>
@@ -44243,7 +44286,7 @@
     </row>
     <row r="976" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A976" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B976" s="2" t="s">
         <v>44</v>
@@ -44252,10 +44295,10 @@
         <v>15</v>
       </c>
       <c r="D976" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E976" s="2" t="s">
         <v>1165</v>
-      </c>
-      <c r="E976" s="2" t="s">
-        <v>1164</v>
       </c>
       <c r="F976" s="2" t="s">
         <v>69</v>
@@ -44284,7 +44327,7 @@
     </row>
     <row r="977" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A977" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B977" s="6" t="s">
         <v>44</v>
@@ -44293,10 +44336,10 @@
         <v>15</v>
       </c>
       <c r="D977" s="6" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="E977" s="6" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="F977" s="6" t="s">
         <v>69</v>
@@ -44325,7 +44368,7 @@
     </row>
     <row r="978" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A978" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B978" s="2" t="s">
         <v>44</v>
@@ -44334,10 +44377,10 @@
         <v>15</v>
       </c>
       <c r="D978" s="2" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="E978" s="2" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="F978" s="2" t="s">
         <v>69</v>
@@ -44366,7 +44409,7 @@
     </row>
     <row r="979" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A979" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B979" s="6" t="s">
         <v>44</v>
@@ -44375,10 +44418,10 @@
         <v>15</v>
       </c>
       <c r="D979" s="6" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="E979" s="6" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="F979" s="6" t="s">
         <v>69</v>
@@ -44407,7 +44450,7 @@
     </row>
     <row r="980" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A980" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B980" s="2" t="s">
         <v>44</v>
@@ -44416,10 +44459,10 @@
         <v>15</v>
       </c>
       <c r="D980" s="2" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="E980" s="2" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="F980" s="2" t="s">
         <v>69</v>
@@ -44448,7 +44491,7 @@
     </row>
     <row r="981" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A981" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B981" s="6" t="s">
         <v>44</v>
@@ -44457,10 +44500,10 @@
         <v>15</v>
       </c>
       <c r="D981" s="6" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="E981" s="6" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="F981" s="6" t="s">
         <v>100</v>
@@ -44489,7 +44532,7 @@
     </row>
     <row r="982" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A982" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B982" s="2" t="s">
         <v>44</v>
@@ -44498,10 +44541,10 @@
         <v>15</v>
       </c>
       <c r="D982" s="2" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E982" s="2" t="s">
         <v>1172</v>
-      </c>
-      <c r="E982" s="2" t="s">
-        <v>1171</v>
       </c>
       <c r="F982" s="2" t="s">
         <v>100</v>
@@ -44530,7 +44573,7 @@
     </row>
     <row r="983" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A983" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B983" s="6" t="s">
         <v>44</v>
@@ -44539,10 +44582,10 @@
         <v>15</v>
       </c>
       <c r="D983" s="6" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="E983" s="6" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="F983" s="6" t="s">
         <v>69</v>
@@ -44571,7 +44614,7 @@
     </row>
     <row r="984" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A984" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B984" s="2" t="s">
         <v>44</v>
@@ -44580,10 +44623,10 @@
         <v>15</v>
       </c>
       <c r="D984" s="2" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="E984" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F984" s="2" t="s">
         <v>25</v>
@@ -44592,7 +44635,7 @@
         <v>1.5</v>
       </c>
       <c r="H984" s="2" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="I984" s="2" t="s">
         <v>19</v>
@@ -44612,7 +44655,7 @@
     </row>
     <row r="985" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A985" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B985" s="6" t="s">
         <v>44</v>
@@ -44621,10 +44664,10 @@
         <v>15</v>
       </c>
       <c r="D985" s="6" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="E985" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F985" s="6" t="s">
         <v>25</v>
@@ -44653,7 +44696,7 @@
     </row>
     <row r="986" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A986" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B986" s="2" t="s">
         <v>44</v>
@@ -44662,10 +44705,10 @@
         <v>15</v>
       </c>
       <c r="D986" s="2" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="E986" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F986" s="2" t="s">
         <v>25</v>
@@ -44694,7 +44737,7 @@
     </row>
     <row r="987" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A987" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B987" s="6" t="s">
         <v>44</v>
@@ -44703,10 +44746,10 @@
         <v>15</v>
       </c>
       <c r="D987" s="6" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="E987" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F987" s="6" t="s">
         <v>25</v>
@@ -44735,7 +44778,7 @@
     </row>
     <row r="988" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A988" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B988" s="2" t="s">
         <v>44</v>
@@ -44744,10 +44787,10 @@
         <v>15</v>
       </c>
       <c r="D988" s="2" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="E988" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F988" s="2" t="s">
         <v>25</v>
@@ -44776,7 +44819,7 @@
     </row>
     <row r="989" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A989" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B989" s="6" t="s">
         <v>44</v>
@@ -44785,10 +44828,10 @@
         <v>15</v>
       </c>
       <c r="D989" s="6" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="E989" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F989" s="6" t="s">
         <v>25</v>
@@ -44817,7 +44860,7 @@
     </row>
     <row r="990" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A990" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B990" s="2" t="s">
         <v>44</v>
@@ -44826,10 +44869,10 @@
         <v>15</v>
       </c>
       <c r="D990" s="2" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="E990" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F990" s="2" t="s">
         <v>25</v>
@@ -44858,7 +44901,7 @@
     </row>
     <row r="991" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A991" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B991" s="6" t="s">
         <v>44</v>
@@ -44867,10 +44910,10 @@
         <v>15</v>
       </c>
       <c r="D991" s="6" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="E991" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F991" s="6" t="s">
         <v>25</v>
@@ -44899,7 +44942,7 @@
     </row>
     <row r="992" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A992" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B992" s="2" t="s">
         <v>44</v>
@@ -44908,10 +44951,10 @@
         <v>15</v>
       </c>
       <c r="D992" s="2" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="E992" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F992" s="2" t="s">
         <v>25</v>
@@ -44940,7 +44983,7 @@
     </row>
     <row r="993" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A993" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B993" s="6" t="s">
         <v>44</v>
@@ -44949,10 +44992,10 @@
         <v>15</v>
       </c>
       <c r="D993" s="6" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="E993" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F993" s="6" t="s">
         <v>25</v>
@@ -44961,7 +45004,7 @@
         <v>2.5</v>
       </c>
       <c r="H993" s="6" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="I993" s="6" t="s">
         <v>19</v>
@@ -44981,7 +45024,7 @@
     </row>
     <row r="994" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A994" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B994" s="2" t="s">
         <v>44</v>
@@ -44990,10 +45033,10 @@
         <v>15</v>
       </c>
       <c r="D994" s="2" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="E994" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F994" s="2" t="s">
         <v>25</v>
@@ -45002,7 +45045,7 @@
         <v>4.5</v>
       </c>
       <c r="H994" s="2" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="I994" s="2" t="s">
         <v>19</v>
@@ -45022,7 +45065,7 @@
     </row>
     <row r="995" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A995" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B995" s="6" t="s">
         <v>44</v>
@@ -45031,10 +45074,10 @@
         <v>15</v>
       </c>
       <c r="D995" s="6" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="E995" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F995" s="6" t="s">
         <v>25</v>
@@ -45063,7 +45106,7 @@
     </row>
     <row r="996" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A996" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B996" s="2" t="s">
         <v>44</v>
@@ -45072,10 +45115,10 @@
         <v>15</v>
       </c>
       <c r="D996" s="2" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="E996" s="2" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="F996" s="2" t="s">
         <v>492</v>
@@ -45104,7 +45147,7 @@
     </row>
     <row r="997" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A997" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B997" s="6" t="s">
         <v>44</v>
@@ -45113,10 +45156,10 @@
         <v>15</v>
       </c>
       <c r="D997" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="E997" s="6" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="F997" s="6" t="s">
         <v>25</v>
@@ -45145,7 +45188,7 @@
     </row>
     <row r="998" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A998" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B998" s="2" t="s">
         <v>44</v>
@@ -45154,10 +45197,10 @@
         <v>15</v>
       </c>
       <c r="D998" s="2" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="E998" s="2" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="F998" s="2" t="s">
         <v>25</v>
@@ -45186,7 +45229,7 @@
     </row>
     <row r="999" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A999" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B999" s="6" t="s">
         <v>44</v>
@@ -45195,10 +45238,10 @@
         <v>15</v>
       </c>
       <c r="D999" s="6" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="E999" s="6" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="F999" s="6" t="s">
         <v>25</v>
@@ -45227,7 +45270,7 @@
     </row>
     <row r="1000" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1000" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1000" s="2" t="s">
         <v>44</v>
@@ -45236,10 +45279,10 @@
         <v>15</v>
       </c>
       <c r="D1000" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="E1000" s="2" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="F1000" s="2" t="s">
         <v>25</v>
@@ -45268,7 +45311,7 @@
     </row>
     <row r="1001" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1001" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1001" s="6" t="s">
         <v>44</v>
@@ -45277,10 +45320,10 @@
         <v>15</v>
       </c>
       <c r="D1001" s="6" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="E1001" s="6" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="F1001" s="6" t="s">
         <v>25</v>
@@ -45309,7 +45352,7 @@
     </row>
     <row r="1002" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1002" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1002" s="2" t="s">
         <v>44</v>
@@ -45318,10 +45361,10 @@
         <v>232</v>
       </c>
       <c r="D1002" s="2" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="E1002" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1002" s="2" t="s">
         <v>25</v>
@@ -45330,7 +45373,7 @@
         <v>2</v>
       </c>
       <c r="H1002" s="2" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="I1002" s="2" t="s">
         <v>19</v>
@@ -45350,7 +45393,7 @@
     </row>
     <row r="1003" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1003" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1003" s="6" t="s">
         <v>44</v>
@@ -45359,10 +45402,10 @@
         <v>232</v>
       </c>
       <c r="D1003" s="6" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="E1003" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1003" s="6" t="s">
         <v>25</v>
@@ -45391,7 +45434,7 @@
     </row>
     <row r="1004" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1004" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1004" s="2" t="s">
         <v>44</v>
@@ -45400,10 +45443,10 @@
         <v>232</v>
       </c>
       <c r="D1004" s="2" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="E1004" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="F1004" s="2" t="s">
         <v>100</v>
@@ -45432,7 +45475,7 @@
     </row>
     <row r="1005" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1005" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1005" s="6" t="s">
         <v>44</v>
@@ -45441,10 +45484,10 @@
         <v>232</v>
       </c>
       <c r="D1005" s="6" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="E1005" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1005" s="6" t="s">
         <v>25</v>
@@ -45473,7 +45516,7 @@
     </row>
     <row r="1006" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1006" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1006" s="2" t="s">
         <v>44</v>
@@ -45482,10 +45525,10 @@
         <v>232</v>
       </c>
       <c r="D1006" s="2" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="E1006" s="2" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="F1006" s="2" t="s">
         <v>69</v>
@@ -45514,7 +45557,7 @@
     </row>
     <row r="1007" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1007" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1007" s="6" t="s">
         <v>44</v>
@@ -45523,10 +45566,10 @@
         <v>232</v>
       </c>
       <c r="D1007" s="6" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="E1007" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1007" s="6" t="s">
         <v>25</v>
@@ -45555,7 +45598,7 @@
     </row>
     <row r="1008" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1008" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1008" s="2" t="s">
         <v>44</v>
@@ -45564,10 +45607,10 @@
         <v>232</v>
       </c>
       <c r="D1008" s="2" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="E1008" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1008" s="2" t="s">
         <v>25</v>
@@ -45596,7 +45639,7 @@
     </row>
     <row r="1009" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1009" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1009" s="6" t="s">
         <v>44</v>
@@ -45605,10 +45648,10 @@
         <v>232</v>
       </c>
       <c r="D1009" s="6" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="E1009" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1009" s="6" t="s">
         <v>25</v>
@@ -45637,7 +45680,7 @@
     </row>
     <row r="1010" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1010" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1010" s="2" t="s">
         <v>44</v>
@@ -45646,10 +45689,10 @@
         <v>232</v>
       </c>
       <c r="D1010" s="2" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="E1010" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1010" s="2" t="s">
         <v>25</v>
@@ -45678,7 +45721,7 @@
     </row>
     <row r="1011" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1011" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1011" s="6" t="s">
         <v>44</v>
@@ -45687,10 +45730,10 @@
         <v>232</v>
       </c>
       <c r="D1011" s="6" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="E1011" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1011" s="6" t="s">
         <v>25</v>
@@ -45719,7 +45762,7 @@
     </row>
     <row r="1012" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1012" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1012" s="2" t="s">
         <v>44</v>
@@ -45728,10 +45771,10 @@
         <v>232</v>
       </c>
       <c r="D1012" s="2" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="E1012" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1012" s="2" t="s">
         <v>25</v>
@@ -45760,7 +45803,7 @@
     </row>
     <row r="1013" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1013" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1013" s="6" t="s">
         <v>44</v>
@@ -45769,10 +45812,10 @@
         <v>232</v>
       </c>
       <c r="D1013" s="6" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="E1013" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1013" s="6" t="s">
         <v>25</v>
@@ -45801,7 +45844,7 @@
     </row>
     <row r="1014" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1014" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1014" s="2" t="s">
         <v>44</v>
@@ -45810,10 +45853,10 @@
         <v>232</v>
       </c>
       <c r="D1014" s="2" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="E1014" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1014" s="2" t="s">
         <v>25</v>
@@ -45842,7 +45885,7 @@
     </row>
     <row r="1015" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1015" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1015" s="6" t="s">
         <v>44</v>
@@ -45851,10 +45894,10 @@
         <v>232</v>
       </c>
       <c r="D1015" s="6" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="E1015" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1015" s="6" t="s">
         <v>25</v>
@@ -45863,7 +45906,7 @@
         <v>10</v>
       </c>
       <c r="H1015" s="6" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="I1015" s="6" t="s">
         <v>19</v>
@@ -45883,7 +45926,7 @@
     </row>
     <row r="1016" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1016" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1016" s="2" t="s">
         <v>44</v>
@@ -45892,10 +45935,10 @@
         <v>232</v>
       </c>
       <c r="D1016" s="2" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="E1016" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1016" s="2" t="s">
         <v>25</v>
@@ -45924,7 +45967,7 @@
     </row>
     <row r="1017" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1017" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1017" s="6" t="s">
         <v>44</v>
@@ -45933,10 +45976,10 @@
         <v>232</v>
       </c>
       <c r="D1017" s="6" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="E1017" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1017" s="6" t="s">
         <v>25</v>
@@ -45965,7 +46008,7 @@
     </row>
     <row r="1018" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1018" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1018" s="2" t="s">
         <v>44</v>
@@ -45974,10 +46017,10 @@
         <v>232</v>
       </c>
       <c r="D1018" s="2" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="E1018" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1018" s="2" t="s">
         <v>25</v>
@@ -46006,7 +46049,7 @@
     </row>
     <row r="1019" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1019" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1019" s="6" t="s">
         <v>44</v>
@@ -46015,10 +46058,10 @@
         <v>232</v>
       </c>
       <c r="D1019" s="6" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="E1019" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1019" s="6" t="s">
         <v>25</v>
@@ -46047,7 +46090,7 @@
     </row>
     <row r="1020" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1020" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1020" s="2" t="s">
         <v>44</v>
@@ -46056,10 +46099,10 @@
         <v>232</v>
       </c>
       <c r="D1020" s="2" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="E1020" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1020" s="2" t="s">
         <v>25</v>
@@ -46088,7 +46131,7 @@
     </row>
     <row r="1021" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1021" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1021" s="6" t="s">
         <v>44</v>
@@ -46097,10 +46140,10 @@
         <v>232</v>
       </c>
       <c r="D1021" s="6" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="E1021" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1021" s="6" t="s">
         <v>25</v>
@@ -46129,7 +46172,7 @@
     </row>
     <row r="1022" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1022" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1022" s="2" t="s">
         <v>44</v>
@@ -46138,10 +46181,10 @@
         <v>232</v>
       </c>
       <c r="D1022" s="2" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="E1022" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1022" s="2" t="s">
         <v>25</v>
@@ -46170,7 +46213,7 @@
     </row>
     <row r="1023" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1023" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1023" s="6" t="s">
         <v>44</v>
@@ -46179,10 +46222,10 @@
         <v>232</v>
       </c>
       <c r="D1023" s="6" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="E1023" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1023" s="6" t="s">
         <v>25</v>
@@ -46211,7 +46254,7 @@
     </row>
     <row r="1024" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1024" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1024" s="2" t="s">
         <v>44</v>
@@ -46220,10 +46263,10 @@
         <v>232</v>
       </c>
       <c r="D1024" s="2" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="E1024" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1024" s="2" t="s">
         <v>25</v>
@@ -46252,7 +46295,7 @@
     </row>
     <row r="1025" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1025" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1025" s="6" t="s">
         <v>44</v>
@@ -46261,10 +46304,10 @@
         <v>232</v>
       </c>
       <c r="D1025" s="6" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="E1025" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1025" s="6" t="s">
         <v>25</v>
@@ -46293,7 +46336,7 @@
     </row>
     <row r="1026" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1026" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1026" s="2" t="s">
         <v>44</v>
@@ -46302,10 +46345,10 @@
         <v>232</v>
       </c>
       <c r="D1026" s="2" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="E1026" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1026" s="2" t="s">
         <v>25</v>
@@ -46334,7 +46377,7 @@
     </row>
     <row r="1027" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1027" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1027" s="6" t="s">
         <v>44</v>
@@ -46343,10 +46386,10 @@
         <v>232</v>
       </c>
       <c r="D1027" s="6" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="E1027" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1027" s="6" t="s">
         <v>25</v>
@@ -46375,7 +46418,7 @@
     </row>
     <row r="1028" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1028" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1028" s="2" t="s">
         <v>44</v>
@@ -46384,10 +46427,10 @@
         <v>232</v>
       </c>
       <c r="D1028" s="2" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="E1028" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1028" s="2" t="s">
         <v>25</v>
@@ -46416,7 +46459,7 @@
     </row>
     <row r="1029" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1029" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1029" s="6" t="s">
         <v>44</v>
@@ -46425,10 +46468,10 @@
         <v>232</v>
       </c>
       <c r="D1029" s="6" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="E1029" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1029" s="6" t="s">
         <v>25</v>
@@ -46457,7 +46500,7 @@
     </row>
     <row r="1030" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1030" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1030" s="2" t="s">
         <v>44</v>
@@ -46466,10 +46509,10 @@
         <v>232</v>
       </c>
       <c r="D1030" s="2" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="E1030" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1030" s="2" t="s">
         <v>25</v>
@@ -46498,7 +46541,7 @@
     </row>
     <row r="1031" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1031" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1031" s="6" t="s">
         <v>44</v>
@@ -46507,10 +46550,10 @@
         <v>232</v>
       </c>
       <c r="D1031" s="6" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="E1031" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1031" s="6" t="s">
         <v>25</v>
@@ -46539,7 +46582,7 @@
     </row>
     <row r="1032" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1032" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1032" s="2" t="s">
         <v>44</v>
@@ -46548,10 +46591,10 @@
         <v>232</v>
       </c>
       <c r="D1032" s="2" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="E1032" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1032" s="2" t="s">
         <v>25</v>
@@ -46580,7 +46623,7 @@
     </row>
     <row r="1033" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1033" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1033" s="6" t="s">
         <v>44</v>
@@ -46589,10 +46632,10 @@
         <v>232</v>
       </c>
       <c r="D1033" s="6" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="E1033" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1033" s="6" t="s">
         <v>25</v>
@@ -46621,7 +46664,7 @@
     </row>
     <row r="1034" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1034" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1034" s="2" t="s">
         <v>44</v>
@@ -46630,10 +46673,10 @@
         <v>232</v>
       </c>
       <c r="D1034" s="2" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="E1034" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1034" s="2" t="s">
         <v>25</v>
@@ -46662,7 +46705,7 @@
     </row>
     <row r="1035" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1035" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1035" s="6" t="s">
         <v>44</v>
@@ -46671,10 +46714,10 @@
         <v>232</v>
       </c>
       <c r="D1035" s="6" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="E1035" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1035" s="6" t="s">
         <v>25</v>
@@ -46703,7 +46746,7 @@
     </row>
     <row r="1036" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1036" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1036" s="2" t="s">
         <v>44</v>
@@ -46712,10 +46755,10 @@
         <v>232</v>
       </c>
       <c r="D1036" s="2" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="E1036" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1036" s="2" t="s">
         <v>25</v>
@@ -46744,7 +46787,7 @@
     </row>
     <row r="1037" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1037" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1037" s="6" t="s">
         <v>44</v>
@@ -46753,10 +46796,10 @@
         <v>232</v>
       </c>
       <c r="D1037" s="6" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="E1037" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1037" s="6" t="s">
         <v>25</v>
@@ -46765,7 +46808,7 @@
         <v>6</v>
       </c>
       <c r="H1037" s="6" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="I1037" s="6" t="s">
         <v>19</v>
@@ -46785,7 +46828,7 @@
     </row>
     <row r="1038" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1038" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1038" s="2" t="s">
         <v>44</v>
@@ -46794,10 +46837,10 @@
         <v>232</v>
       </c>
       <c r="D1038" s="2" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="E1038" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1038" s="2" t="s">
         <v>25</v>
@@ -46826,7 +46869,7 @@
     </row>
     <row r="1039" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1039" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1039" s="6" t="s">
         <v>44</v>
@@ -46835,10 +46878,10 @@
         <v>232</v>
       </c>
       <c r="D1039" s="6" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="E1039" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1039" s="6" t="s">
         <v>25</v>
@@ -46867,7 +46910,7 @@
     </row>
     <row r="1040" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1040" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1040" s="2" t="s">
         <v>44</v>
@@ -46876,10 +46919,10 @@
         <v>232</v>
       </c>
       <c r="D1040" s="2" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="E1040" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1040" s="2" t="s">
         <v>25</v>
@@ -46908,7 +46951,7 @@
     </row>
     <row r="1041" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1041" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1041" s="6" t="s">
         <v>44</v>
@@ -46917,10 +46960,10 @@
         <v>232</v>
       </c>
       <c r="D1041" s="6" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="E1041" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1041" s="6" t="s">
         <v>25</v>
@@ -46949,7 +46992,7 @@
     </row>
     <row r="1042" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1042" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1042" s="2" t="s">
         <v>44</v>
@@ -46958,10 +47001,10 @@
         <v>232</v>
       </c>
       <c r="D1042" s="2" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="E1042" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1042" s="2" t="s">
         <v>25</v>
@@ -46990,7 +47033,7 @@
     </row>
     <row r="1043" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1043" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1043" s="6" t="s">
         <v>44</v>
@@ -46999,10 +47042,10 @@
         <v>232</v>
       </c>
       <c r="D1043" s="6" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="E1043" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1043" s="6" t="s">
         <v>25</v>
@@ -47031,7 +47074,7 @@
     </row>
     <row r="1044" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1044" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1044" s="2" t="s">
         <v>44</v>
@@ -47040,10 +47083,10 @@
         <v>232</v>
       </c>
       <c r="D1044" s="2" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="E1044" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1044" s="2" t="s">
         <v>25</v>
@@ -47072,7 +47115,7 @@
     </row>
     <row r="1045" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1045" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1045" s="6" t="s">
         <v>44</v>
@@ -47081,10 +47124,10 @@
         <v>232</v>
       </c>
       <c r="D1045" s="6" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="E1045" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1045" s="6" t="s">
         <v>25</v>
@@ -47113,7 +47156,7 @@
     </row>
     <row r="1046" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1046" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1046" s="2" t="s">
         <v>44</v>
@@ -47122,10 +47165,10 @@
         <v>232</v>
       </c>
       <c r="D1046" s="2" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="E1046" s="2" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="F1046" s="2" t="s">
         <v>69</v>
@@ -47154,7 +47197,7 @@
     </row>
     <row r="1047" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1047" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1047" s="6" t="s">
         <v>44</v>
@@ -47163,10 +47206,10 @@
         <v>232</v>
       </c>
       <c r="D1047" s="6" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="E1047" s="6" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="F1047" s="6" t="s">
         <v>186</v>
@@ -47195,7 +47238,7 @@
     </row>
     <row r="1048" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1048" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1048" s="2" t="s">
         <v>44</v>
@@ -47204,10 +47247,10 @@
         <v>232</v>
       </c>
       <c r="D1048" s="2" t="s">
+        <v>1247</v>
+      </c>
+      <c r="E1048" s="2" t="s">
         <v>1246</v>
-      </c>
-      <c r="E1048" s="2" t="s">
-        <v>1245</v>
       </c>
       <c r="F1048" s="2" t="s">
         <v>186</v>
@@ -47236,7 +47279,7 @@
     </row>
     <row r="1049" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1049" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1049" s="6" t="s">
         <v>44</v>
@@ -47245,10 +47288,10 @@
         <v>232</v>
       </c>
       <c r="D1049" s="6" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="E1049" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1049" s="6" t="s">
         <v>25</v>
@@ -47257,7 +47300,7 @@
         <v>2</v>
       </c>
       <c r="H1049" s="6" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="I1049" s="6" t="s">
         <v>19</v>
@@ -47277,7 +47320,7 @@
     </row>
     <row r="1050" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1050" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1050" s="2" t="s">
         <v>44</v>
@@ -47286,10 +47329,10 @@
         <v>232</v>
       </c>
       <c r="D1050" s="2" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="E1050" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1050" s="2" t="s">
         <v>25</v>
@@ -47298,7 +47341,7 @@
         <v>4</v>
       </c>
       <c r="H1050" s="2" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="I1050" s="2" t="s">
         <v>19</v>
@@ -47318,7 +47361,7 @@
     </row>
     <row r="1051" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1051" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1051" s="6" t="s">
         <v>44</v>
@@ -47327,10 +47370,10 @@
         <v>232</v>
       </c>
       <c r="D1051" s="6" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="E1051" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1051" s="6" t="s">
         <v>25</v>
@@ -47359,7 +47402,7 @@
     </row>
     <row r="1052" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1052" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1052" s="2" t="s">
         <v>44</v>
@@ -47368,10 +47411,10 @@
         <v>232</v>
       </c>
       <c r="D1052" s="2" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="E1052" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1052" s="2" t="s">
         <v>25</v>
@@ -47380,7 +47423,7 @@
         <v>8</v>
       </c>
       <c r="H1052" s="2" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="I1052" s="2" t="s">
         <v>19</v>
@@ -47400,7 +47443,7 @@
     </row>
     <row r="1053" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1053" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1053" s="6" t="s">
         <v>44</v>
@@ -47409,10 +47452,10 @@
         <v>232</v>
       </c>
       <c r="D1053" s="6" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="E1053" s="6" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="F1053" s="6" t="s">
         <v>69</v>
@@ -47441,7 +47484,7 @@
     </row>
     <row r="1054" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1054" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1054" s="2" t="s">
         <v>44</v>
@@ -47450,10 +47493,10 @@
         <v>232</v>
       </c>
       <c r="D1054" s="2" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="E1054" s="2" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="F1054" s="2" t="s">
         <v>558</v>
@@ -47482,7 +47525,7 @@
     </row>
     <row r="1055" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1055" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1055" s="6" t="s">
         <v>44</v>
@@ -47491,10 +47534,10 @@
         <v>232</v>
       </c>
       <c r="D1055" s="6" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="E1055" s="6" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="F1055" s="6" t="s">
         <v>100</v>
@@ -47523,7 +47566,7 @@
     </row>
     <row r="1056" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1056" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1056" s="2" t="s">
         <v>44</v>
@@ -47532,10 +47575,10 @@
         <v>232</v>
       </c>
       <c r="D1056" s="2" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="E1056" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1056" s="2" t="s">
         <v>25</v>
@@ -47544,7 +47587,7 @@
         <v>2</v>
       </c>
       <c r="H1056" s="2" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="I1056" s="2" t="s">
         <v>19</v>
@@ -47564,7 +47607,7 @@
     </row>
     <row r="1057" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1057" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1057" s="6" t="s">
         <v>44</v>
@@ -47573,10 +47616,10 @@
         <v>232</v>
       </c>
       <c r="D1057" s="6" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="E1057" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1057" s="6" t="s">
         <v>25</v>
@@ -47605,7 +47648,7 @@
     </row>
     <row r="1058" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1058" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1058" s="2" t="s">
         <v>44</v>
@@ -47614,10 +47657,10 @@
         <v>232</v>
       </c>
       <c r="D1058" s="2" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="E1058" s="2" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="F1058" s="2" t="s">
         <v>487</v>
@@ -47646,7 +47689,7 @@
     </row>
     <row r="1059" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1059" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1059" s="6" t="s">
         <v>44</v>
@@ -47655,10 +47698,10 @@
         <v>232</v>
       </c>
       <c r="D1059" s="6" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="E1059" s="6" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="F1059" s="6" t="s">
         <v>25</v>
@@ -47687,7 +47730,7 @@
     </row>
     <row r="1060" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1060" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1060" s="2" t="s">
         <v>44</v>
@@ -47696,10 +47739,10 @@
         <v>232</v>
       </c>
       <c r="D1060" s="2" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="E1060" s="2" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="F1060" s="2" t="s">
         <v>25</v>
@@ -47728,7 +47771,7 @@
     </row>
     <row r="1061" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1061" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1061" s="6" t="s">
         <v>44</v>
@@ -47737,10 +47780,10 @@
         <v>232</v>
       </c>
       <c r="D1061" s="6" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="E1061" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1061" s="6" t="s">
         <v>25</v>
@@ -47749,7 +47792,7 @@
         <v>2</v>
       </c>
       <c r="H1061" s="6" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="I1061" s="6" t="s">
         <v>19</v>
@@ -47769,7 +47812,7 @@
     </row>
     <row r="1062" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1062" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1062" s="2" t="s">
         <v>44</v>
@@ -47778,10 +47821,10 @@
         <v>232</v>
       </c>
       <c r="D1062" s="2" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="E1062" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1062" s="2" t="s">
         <v>25</v>
@@ -47790,7 +47833,7 @@
         <v>4</v>
       </c>
       <c r="H1062" s="2" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="I1062" s="2" t="s">
         <v>19</v>
@@ -47810,7 +47853,7 @@
     </row>
     <row r="1063" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1063" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1063" s="6" t="s">
         <v>44</v>
@@ -47819,10 +47862,10 @@
         <v>232</v>
       </c>
       <c r="D1063" s="6" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="E1063" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1063" s="6" t="s">
         <v>25</v>
@@ -47831,7 +47874,7 @@
         <v>2</v>
       </c>
       <c r="H1063" s="6" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="I1063" s="6" t="s">
         <v>19</v>
@@ -47851,7 +47894,7 @@
     </row>
     <row r="1064" ht="16" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1064" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B1064" s="2" t="s">
         <v>44</v>
@@ -47860,10 +47903,10 @@
         <v>232</v>
       </c>
       <c r="D1064" s="2" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="E1064" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="F1064" s="2" t="s">
         <v>25</v>
